--- a/ig/Atelier-amelioration-formelle/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/ig/Atelier-amelioration-formelle/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T07:58:37+00:00</t>
+    <t>2023-05-12T08:17:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/Atelier-amelioration-formelle/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/ig/Atelier-amelioration-formelle/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T08:17:55+00:00</t>
+    <t>2023-05-12T15:07:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/Atelier-amelioration-formelle/StructureDefinition-mesures-fr-observation-heartrate.xlsx
+++ b/ig/Atelier-amelioration-formelle/StructureDefinition-mesures-fr-observation-heartrate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T15:07:01+00:00</t>
+    <t>2023-05-23T14:13:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
